--- a/data.mn/public/datasets/mongolbank-deposit-rate-fx-monthly.xlsx
+++ b/data.mn/public/datasets/mongolbank-deposit-rate-fx-monthly.xlsx
@@ -416,6 +416,28 @@
   </sheetPr>
   <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="6" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -520,14 +542,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
       <c r="E2" t="n">
         <v>4.28</v>
       </c>
@@ -578,14 +595,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
       <c r="E3" t="n">
         <v>4.94</v>
       </c>
@@ -631,15 +643,14 @@
       <c r="S3" t="n">
         <v>3.8</v>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>4.21</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
       <c r="C4" t="n">
         <v>6.32</v>
       </c>
@@ -656,13 +667,13 @@
         <v>6.99</v>
       </c>
       <c r="H4" t="n">
-        <v>5.600000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="I4" t="n">
         <v>5.99</v>
       </c>
       <c r="J4" t="n">
-        <v>6.600000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="K4" t="n">
         <v>6.16</v>
@@ -691,17 +702,14 @@
       <c r="S4" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>4.25</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
       <c r="E5" t="n">
         <v>4.83</v>
       </c>
@@ -730,7 +738,7 @@
         <v>4.95</v>
       </c>
       <c r="N5" t="n">
-        <v>4.568002</v>
+        <v>4.57</v>
       </c>
       <c r="O5" t="n">
         <v>2.6</v>
@@ -747,17 +755,14 @@
       <c r="S5" t="n">
         <v>4.03</v>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
       <c r="E6" t="n">
         <v>4.97</v>
       </c>
@@ -803,15 +808,14 @@
       <c r="S6" t="n">
         <v>4.01</v>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>4.28</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
@@ -825,10 +829,10 @@
         <v>5.9</v>
       </c>
       <c r="G7" t="n">
-        <v>5.600000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="H7" t="n">
-        <v>5.600000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="I7" t="n">
         <v>6.32</v>
@@ -846,7 +850,7 @@
         <v>4.95</v>
       </c>
       <c r="N7" t="n">
-        <v>4.32605</v>
+        <v>4.33</v>
       </c>
       <c r="O7" t="n">
         <v>2.48</v>
@@ -863,17 +867,14 @@
       <c r="S7" t="n">
         <v>4</v>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>4.19</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
       <c r="E8" t="n">
         <v>4.88</v>
       </c>
@@ -902,7 +903,7 @@
         <v>4.98</v>
       </c>
       <c r="N8" t="n">
-        <v>4.239669999999999</v>
+        <v>4.24</v>
       </c>
       <c r="O8" t="n">
         <v>2.37</v>
@@ -919,17 +920,14 @@
       <c r="S8" t="n">
         <v>4.04</v>
       </c>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>4.13</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
       <c r="E9" t="n">
         <v>4.68</v>
       </c>
@@ -946,7 +944,7 @@
         <v>6.48</v>
       </c>
       <c r="J9" t="n">
-        <v>6.350000000000001</v>
+        <v>6.35</v>
       </c>
       <c r="K9" t="n">
         <v>5.47</v>
@@ -958,7 +956,7 @@
         <v>4.99</v>
       </c>
       <c r="N9" t="n">
-        <v>4.134897</v>
+        <v>4.13</v>
       </c>
       <c r="O9" t="n">
         <v>2.22</v>
@@ -975,15 +973,11 @@
       <c r="S9" t="n">
         <v>4.05</v>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
       <c r="C10" t="n">
         <v>6.99</v>
       </c>
@@ -1035,17 +1029,11 @@
       <c r="S10" t="n">
         <v>4.15</v>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
       <c r="E11" t="n">
         <v>4.72</v>
       </c>
@@ -1091,17 +1079,11 @@
       <c r="S11" t="n">
         <v>4.24</v>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
       <c r="E12" t="n">
         <v>4.66</v>
       </c>
@@ -1147,13 +1129,10 @@
       <c r="S12" t="n">
         <v>4.25</v>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="n">
         <v>7.4</v>
@@ -1177,7 +1156,7 @@
         <v>5.76</v>
       </c>
       <c r="I13" t="n">
-        <v>6.600000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
         <v>6</v>
@@ -1209,7 +1188,6 @@
       <c r="S13" t="n">
         <v>4.19</v>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1224,6 +1202,28 @@
   </sheetPr>
   <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="6" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1328,14 +1328,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
       <c r="E2" t="n">
         <v>4.28</v>
       </c>
@@ -1386,14 +1381,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
       <c r="E3" t="n">
         <v>4.94</v>
       </c>
@@ -1439,15 +1429,14 @@
       <c r="S3" t="n">
         <v>3.8</v>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>4.21</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
       <c r="C4" t="n">
         <v>6.32</v>
       </c>
@@ -1464,13 +1453,13 @@
         <v>6.99</v>
       </c>
       <c r="H4" t="n">
-        <v>5.600000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="I4" t="n">
         <v>5.99</v>
       </c>
       <c r="J4" t="n">
-        <v>6.600000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="K4" t="n">
         <v>6.16</v>
@@ -1499,17 +1488,14 @@
       <c r="S4" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>4.25</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
       <c r="E5" t="n">
         <v>4.83</v>
       </c>
@@ -1538,7 +1524,7 @@
         <v>4.95</v>
       </c>
       <c r="N5" t="n">
-        <v>4.568002</v>
+        <v>4.57</v>
       </c>
       <c r="O5" t="n">
         <v>2.6</v>
@@ -1555,17 +1541,14 @@
       <c r="S5" t="n">
         <v>4.03</v>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
       <c r="E6" t="n">
         <v>4.97</v>
       </c>
@@ -1611,15 +1594,14 @@
       <c r="S6" t="n">
         <v>4.01</v>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>4.28</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
@@ -1633,10 +1615,10 @@
         <v>5.9</v>
       </c>
       <c r="G7" t="n">
-        <v>5.600000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="H7" t="n">
-        <v>5.600000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="I7" t="n">
         <v>6.32</v>
@@ -1654,7 +1636,7 @@
         <v>4.95</v>
       </c>
       <c r="N7" t="n">
-        <v>4.32605</v>
+        <v>4.33</v>
       </c>
       <c r="O7" t="n">
         <v>2.48</v>
@@ -1671,17 +1653,14 @@
       <c r="S7" t="n">
         <v>4</v>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>4.19</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
       <c r="E8" t="n">
         <v>4.88</v>
       </c>
@@ -1710,7 +1689,7 @@
         <v>4.98</v>
       </c>
       <c r="N8" t="n">
-        <v>4.239669999999999</v>
+        <v>4.24</v>
       </c>
       <c r="O8" t="n">
         <v>2.37</v>
@@ -1727,17 +1706,14 @@
       <c r="S8" t="n">
         <v>4.04</v>
       </c>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>4.13</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
       <c r="E9" t="n">
         <v>4.68</v>
       </c>
@@ -1754,7 +1730,7 @@
         <v>6.48</v>
       </c>
       <c r="J9" t="n">
-        <v>6.350000000000001</v>
+        <v>6.35</v>
       </c>
       <c r="K9" t="n">
         <v>5.47</v>
@@ -1766,7 +1742,7 @@
         <v>4.99</v>
       </c>
       <c r="N9" t="n">
-        <v>4.134897</v>
+        <v>4.13</v>
       </c>
       <c r="O9" t="n">
         <v>2.22</v>
@@ -1783,15 +1759,11 @@
       <c r="S9" t="n">
         <v>4.05</v>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
       <c r="C10" t="n">
         <v>6.99</v>
       </c>
@@ -1843,17 +1815,11 @@
       <c r="S10" t="n">
         <v>4.15</v>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
       <c r="E11" t="n">
         <v>4.72</v>
       </c>
@@ -1899,17 +1865,11 @@
       <c r="S11" t="n">
         <v>4.24</v>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
       <c r="E12" t="n">
         <v>4.66</v>
       </c>
@@ -1955,13 +1915,10 @@
       <c r="S12" t="n">
         <v>4.25</v>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="n">
         <v>7.4</v>
@@ -1985,7 +1942,7 @@
         <v>5.76</v>
       </c>
       <c r="I13" t="n">
-        <v>6.600000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
         <v>6</v>
@@ -2017,7 +1974,6 @@
       <c r="S13" t="n">
         <v>4.19</v>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
